--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_74_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_74_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>8</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>2</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>2</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3099,16 +3099,16 @@
         <v>24</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>121</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X37" t="n">
         <v>6</v>
@@ -5664,7 +5664,7 @@
         <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>-1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>65</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>15</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_74_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_74_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1935,14 +1935,14 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
         <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,14 +4696,14 @@
         <v>4</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="AA48" t="n">
